--- a/Chấm công/Chấm công tổng hợp/bảng chấm công 15 đến 31 tháng 01 năm 2026.xlsx
+++ b/Chấm công/Chấm công tổng hợp/bảng chấm công 15 đến 31 tháng 01 năm 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Chấm công\Chấm công tổng hợp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA90AA9-C6F3-41B8-A8E7-766F73687A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FB530B-D616-415C-8F5A-F2AE06468659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7C654F61-D3F6-46B9-9944-3469B6AD53BB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="81">
   <si>
     <t>CÔNG TY TNHH MTV VẬN TẢI VÀ DU LỊCH MINH HẢI</t>
   </si>
@@ -281,13 +281,19 @@
   </si>
   <si>
     <t>CÒN LÀM</t>
+  </si>
+  <si>
+    <t>TIỀN ĐIỆN</t>
+  </si>
+  <si>
+    <t>TỔNG TIỀN ĐIỆN + CHÊNH LỆCH 10%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="13"/>
       <color theme="1"/>
@@ -374,6 +380,13 @@
     <font>
       <b/>
       <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color rgb="FFFFFF00"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -517,7 +530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -604,37 +617,7 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -650,6 +633,51 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -966,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1272D7-D111-44D1-8D7B-C8C37D80B9DE}">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -979,14 +1007,14 @@
     <col min="8" max="8" width="14.33203125" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" customWidth="1"/>
     <col min="10" max="10" width="19.5546875" customWidth="1"/>
-    <col min="11" max="11" width="19.33203125" customWidth="1"/>
-    <col min="12" max="12" width="19.109375" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="20.44140625" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
+    <col min="11" max="13" width="19.33203125" customWidth="1"/>
+    <col min="14" max="14" width="19.109375" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="20.44140625" customWidth="1"/>
+    <col min="17" max="17" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="27.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="27.75" x14ac:dyDescent="0.25">
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
@@ -996,37 +1024,33 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="G2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="N2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="7">
-        <v>1700000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L3" s="28" t="s">
+      <c r="O2" s="49"/>
+    </row>
+    <row r="3" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N3" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-    </row>
-    <row r="5" spans="1:15" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="O3" s="50"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+    </row>
+    <row r="5" spans="1:17" ht="82.5" x14ac:dyDescent="0.25">
       <c r="B5" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="32"/>
+      <c r="D5" s="40"/>
       <c r="E5" s="26" t="s">
         <v>4</v>
       </c>
@@ -1048,21 +1072,27 @@
       <c r="K5" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="26" t="s">
+      <c r="L5" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="M5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="N5" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="O5" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="26" t="s">
+      <c r="P5" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="26" t="s">
+      <c r="Q5" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+    <row r="6" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="41" t="s">
         <v>62</v>
       </c>
       <c r="B6" s="13">
@@ -1080,7 +1110,7 @@
       <c r="F6" s="20">
         <v>29549000</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="34">
         <v>13189000</v>
       </c>
       <c r="H6" s="14">
@@ -1093,25 +1123,28 @@
       <c r="J6" s="14">
         <v>13338000</v>
       </c>
-      <c r="K6" s="20">
-        <f t="shared" ref="K6:K15" si="0">I6*10%</f>
-        <v>-41100</v>
-      </c>
-      <c r="L6" s="29" t="s">
+      <c r="K6" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="M6" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N6" s="17" t="s">
+      <c r="O6" s="13"/>
+      <c r="P6" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="O6" s="46" t="s">
+      <c r="Q6" s="36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
+    <row r="7" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="42"/>
       <c r="B7" s="13">
         <f>B6+1</f>
         <v>2</v>
@@ -1128,38 +1161,41 @@
       <c r="F7" s="20">
         <v>24901000</v>
       </c>
-      <c r="G7" s="44">
-        <v>15725000</v>
+      <c r="G7" s="34">
+        <v>12160000</v>
       </c>
       <c r="H7" s="14">
         <v>13600000</v>
       </c>
       <c r="I7" s="14">
-        <f t="shared" ref="I7:I15" si="1">G7-H7</f>
-        <v>2125000</v>
+        <f t="shared" ref="I7:I15" si="0">G7-H7</f>
+        <v>-1440000</v>
       </c>
       <c r="J7" s="14">
         <v>10292000</v>
       </c>
-      <c r="K7" s="20">
-        <f t="shared" si="0"/>
-        <v>212500</v>
-      </c>
-      <c r="L7" s="29" t="s">
+      <c r="K7" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="16" t="s">
+      <c r="O7" s="13"/>
+      <c r="P7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="O7" s="46" t="s">
+      <c r="Q7" s="36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="38"/>
+    <row r="8" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="42"/>
       <c r="B8" s="13">
         <f>B7+1</f>
         <v>3</v>
@@ -1176,38 +1212,42 @@
       <c r="F8" s="20">
         <v>25400000</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="34">
         <v>14220000</v>
       </c>
       <c r="H8" s="14">
         <v>13600000</v>
       </c>
       <c r="I8" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>620000</v>
       </c>
       <c r="J8" s="14">
         <v>10891000</v>
       </c>
       <c r="K8" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K7:M15" si="1">I8*10%</f>
         <v>62000</v>
       </c>
-      <c r="L8" s="45" t="s">
+      <c r="L8" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="48">
+        <v>62000</v>
+      </c>
+      <c r="N8" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="M8" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="46" t="s">
+      <c r="O8" s="13"/>
+      <c r="P8" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q8" s="36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="38"/>
+    <row r="9" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="42"/>
       <c r="B9" s="13">
         <f t="shared" ref="B9:B18" si="2">B8+1</f>
         <v>4</v>
@@ -1224,38 +1264,41 @@
       <c r="F9" s="20">
         <v>27158000</v>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="34">
         <v>11810000</v>
       </c>
       <c r="H9" s="14">
         <v>13600000</v>
       </c>
       <c r="I9" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-1790000</v>
       </c>
       <c r="J9" s="14">
         <v>12197000</v>
       </c>
-      <c r="K9" s="20">
-        <f t="shared" si="0"/>
-        <v>-179000</v>
-      </c>
-      <c r="L9" s="29" t="s">
+      <c r="K9" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="N9" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="M9" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" s="17" t="s">
+      <c r="O9" s="13"/>
+      <c r="P9" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O9" s="46" t="s">
+      <c r="Q9" s="36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="38"/>
+    <row r="10" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="42"/>
       <c r="B10" s="13">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -1272,38 +1315,42 @@
       <c r="F10" s="20">
         <v>29190000</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="34">
         <v>14870000</v>
       </c>
       <c r="H10" s="14">
         <v>13600000</v>
       </c>
       <c r="I10" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1270000</v>
       </c>
       <c r="J10" s="14">
         <v>12842000</v>
       </c>
       <c r="K10" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>127000</v>
       </c>
-      <c r="L10" s="29" t="s">
+      <c r="L10" s="48">
+        <v>500000</v>
+      </c>
+      <c r="M10" s="48">
+        <v>627000</v>
+      </c>
+      <c r="N10" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="M10" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" s="17" t="s">
+      <c r="O10" s="13"/>
+      <c r="P10" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="O10" s="47" t="s">
+      <c r="Q10" s="37" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="38"/>
+    <row r="11" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="42"/>
       <c r="B11" s="13">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -1320,38 +1367,42 @@
       <c r="F11" s="20">
         <v>49145000</v>
       </c>
-      <c r="G11" s="44">
+      <c r="G11" s="34">
         <v>29240000</v>
       </c>
       <c r="H11" s="14">
         <v>13600000</v>
       </c>
       <c r="I11" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>15640000</v>
       </c>
       <c r="J11" s="14">
         <v>21515000</v>
       </c>
-      <c r="K11" s="20">
-        <f t="shared" si="0"/>
+      <c r="K11" s="51">
+        <f t="shared" si="1"/>
         <v>1564000</v>
       </c>
-      <c r="L11" s="45" t="s">
+      <c r="L11" s="48">
+        <v>500000</v>
+      </c>
+      <c r="M11" s="52">
+        <v>2064000</v>
+      </c>
+      <c r="N11" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="M11" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="O11" s="46" t="s">
+      <c r="O11" s="13"/>
+      <c r="P11" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="38"/>
+    <row r="12" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="42"/>
       <c r="B12" s="13">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -1368,46 +1419,50 @@
       <c r="F12" s="20">
         <v>25477000</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="34">
         <v>14607000</v>
       </c>
       <c r="H12" s="14">
         <v>13600000</v>
       </c>
       <c r="I12" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1007000</v>
       </c>
       <c r="J12" s="14">
         <v>11163000</v>
       </c>
       <c r="K12" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100700</v>
       </c>
-      <c r="L12" s="29" t="s">
+      <c r="L12" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" s="48">
+        <v>100700</v>
+      </c>
+      <c r="N12" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="M12" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N12" s="17" t="s">
+      <c r="O12" s="13"/>
+      <c r="P12" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="O12" s="47" t="s">
+      <c r="Q12" s="37" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="38"/>
+    <row r="13" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="42"/>
       <c r="B13" s="13">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="33" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -1416,46 +1471,50 @@
       <c r="F13" s="20">
         <v>30275000</v>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="34">
         <v>15725000</v>
       </c>
       <c r="H13" s="14">
         <v>13600000</v>
       </c>
       <c r="I13" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2125000</v>
       </c>
       <c r="J13" s="7">
         <v>13446000</v>
       </c>
       <c r="K13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>212500</v>
       </c>
-      <c r="L13" s="29" t="s">
+      <c r="L13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="48">
+        <v>212500</v>
+      </c>
+      <c r="N13" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="M13" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N13" s="17" t="s">
+      <c r="O13" s="13"/>
+      <c r="P13" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O13" s="47" t="s">
+      <c r="Q13" s="37" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="40"/>
+    <row r="14" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="43"/>
       <c r="B14" s="13">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="33" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -1464,45 +1523,48 @@
       <c r="F14" s="20">
         <v>16108000</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="34">
         <v>9810000</v>
       </c>
       <c r="H14" s="14">
         <v>13600000</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-3790000</v>
       </c>
       <c r="J14" s="7">
         <v>7078000</v>
       </c>
-      <c r="K14" s="20">
-        <f t="shared" si="0"/>
-        <v>-379000</v>
-      </c>
-      <c r="L14" s="45" t="s">
+      <c r="K14" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="O14" s="46" t="s">
+      <c r="O14" s="13"/>
+      <c r="P14" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q14" s="36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="13">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="43" t="s">
+      <c r="D15" s="33" t="s">
         <v>75</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -1511,92 +1573,102 @@
       <c r="F15" s="20">
         <v>34465000</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="34">
         <v>13970000</v>
       </c>
       <c r="H15" s="14">
         <v>13600000</v>
       </c>
       <c r="I15" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>370000</v>
       </c>
       <c r="J15" s="7">
         <v>15824000</v>
       </c>
       <c r="K15" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>37000</v>
       </c>
-      <c r="L15" s="45" t="s">
+      <c r="L15" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="48">
+        <v>37000</v>
+      </c>
+      <c r="N15" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="O15" s="46" t="s">
+      <c r="O15" s="13"/>
+      <c r="P15" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q15" s="36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="13">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="39"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="20"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-    </row>
-    <row r="17" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
+    </row>
+    <row r="17" spans="2:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="13">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="39"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="30"/>
       <c r="F17" s="20"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="39"/>
-    </row>
-    <row r="18" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="30"/>
+    </row>
+    <row r="18" spans="2:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="13">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="39"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="30"/>
       <c r="F18" s="20"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1657,17 +1729,17 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
     </row>
     <row r="5" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
       <c r="B5" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="32"/>
+      <c r="D5" s="40"/>
       <c r="E5" s="26" t="s">
         <v>4</v>
       </c>
@@ -1697,7 +1769,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="44" t="s">
         <v>64</v>
       </c>
       <c r="B6" s="13">
@@ -1739,7 +1811,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="34"/>
+      <c r="A7" s="45"/>
       <c r="B7" s="13">
         <f>B6+1</f>
         <v>2</v>
@@ -1778,7 +1850,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34"/>
+      <c r="A8" s="45"/>
       <c r="B8" s="13">
         <f t="shared" ref="B8" si="1">B7+1</f>
         <v>3</v>
@@ -1876,17 +1948,17 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
     </row>
     <row r="5" spans="1:13" ht="49.5" x14ac:dyDescent="0.25">
       <c r="B5" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="32"/>
+      <c r="D5" s="40"/>
       <c r="E5" s="26" t="s">
         <v>4</v>
       </c>
@@ -1916,7 +1988,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="46" t="s">
         <v>63</v>
       </c>
       <c r="B6" s="23">
@@ -1956,7 +2028,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="36"/>
+      <c r="A7" s="47"/>
       <c r="B7" s="23">
         <v>2</v>
       </c>
@@ -1994,7 +2066,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="36"/>
+      <c r="A8" s="47"/>
       <c r="B8" s="13">
         <f>B7+1</f>
         <v>3</v>
